--- a/output/pdf_financials_xlsx/FBR.H.xlsx
+++ b/output/pdf_financials_xlsx/FBR.H.xlsx
@@ -1148,25 +1148,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.026521</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.047326</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.141978</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.101904</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.108991</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.09013699999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.065068</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -2311,25 +2311,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.081549</v>
+        <v>-0.10807</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.038472</v>
+        <v>-0.085798</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.160814</v>
+        <v>-0.302792</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.002287</v>
+        <v>-0.099617</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.229853</v>
+        <v>0.120862</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.023974</v>
+        <v>-0.114111</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.131636</v>
+        <v>-0.196704</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2457,25 +2457,25 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.081549</v>
+        <v>-0.10807</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.038472</v>
+        <v>-0.085798</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.160814</v>
+        <v>-0.302792</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.002287</v>
+        <v>-0.099617</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.229853</v>
+        <v>0.120862</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.023974</v>
+        <v>-0.114111</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.131636</v>
+        <v>-0.196704</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -32876,7 +32876,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -34326,7 +34326,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
